--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260924.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260924.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -967,7 +967,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2219,7 +2219,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2307,7 +2307,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2873,7 +2873,7 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14487,7 +14487,7 @@
       <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17585,7 +17585,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18509,7 +18509,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19213,7 +19213,7 @@
       <c r="AD164" t="inlineStr"/>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19831,7 +19831,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19953,7 +19953,7 @@
       <c r="AD170" t="inlineStr"/>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20065,7 +20065,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21197,7 +21197,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21989,7 +21989,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22339,7 +22339,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22581,7 +22581,7 @@
       <c r="AD193" t="inlineStr"/>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22707,7 +22707,7 @@
       <c r="AD194" t="inlineStr"/>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22833,7 +22833,7 @@
       <c r="AD195" t="inlineStr"/>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23063,7 +23063,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23411,7 +23411,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23641,7 +23641,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24667,7 +24667,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24779,7 +24779,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24889,7 +24889,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26281,7 +26281,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26505,7 +26505,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26615,7 +26615,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26725,7 +26725,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27171,7 +27171,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27403,7 +27403,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27513,7 +27513,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28091,7 +28091,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28423,7 +28423,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28769,7 +28769,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28885,7 +28885,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29001,7 +29001,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29111,7 +29111,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30015,7 +30015,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30225,7 +30225,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30563,7 +30563,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30673,7 +30673,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30793,7 +30793,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30905,7 +30905,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31015,7 +31015,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31127,7 +31127,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31243,7 +31243,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31691,7 +31691,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31817,7 +31817,7 @@
       <c r="AD274" t="inlineStr"/>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32057,7 +32057,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32257,7 +32257,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32371,7 +32371,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32485,7 +32485,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32817,7 +32817,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32929,7 +32929,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33043,7 +33043,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33157,7 +33157,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33271,7 +33271,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33531,7 +33531,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33659,7 +33659,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33787,7 +33787,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34011,7 +34011,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34121,7 +34121,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34231,7 +34231,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34597,7 +34597,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34821,7 +34821,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35051,7 +35051,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35175,7 +35175,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35423,7 +35423,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35651,7 +35651,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35763,7 +35763,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36019,7 +36019,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36131,7 +36131,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36353,7 +36353,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36463,7 +36463,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36579,7 +36579,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36691,7 +36691,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36811,7 +36811,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36939,7 +36939,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37267,7 +37267,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37741,7 +37741,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37851,7 +37851,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37961,7 +37961,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38071,7 +38071,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38191,7 +38191,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38411,7 +38411,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38521,7 +38521,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38641,7 +38641,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38761,7 +38761,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39001,7 +39001,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39233,7 +39233,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39461,7 +39461,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39577,7 +39577,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39697,7 +39697,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39809,7 +39809,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39925,7 +39925,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40041,7 +40041,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40273,7 +40273,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40387,7 +40387,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40619,7 +40619,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40735,7 +40735,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40961,7 +40961,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41073,7 +41073,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41295,7 +41295,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41407,7 +41407,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41519,7 +41519,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41639,7 +41639,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41767,7 +41767,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41887,7 +41887,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42127,7 +42127,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42237,7 +42237,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42347,7 +42347,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42681,7 +42681,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42797,7 +42797,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42907,7 +42907,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43019,7 +43019,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43129,7 +43129,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43239,7 +43239,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43367,7 +43367,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43607,7 +43607,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43719,7 +43719,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43829,7 +43829,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43939,7 +43939,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44049,7 +44049,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44271,7 +44271,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44399,7 +44399,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44621,7 +44621,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44731,7 +44731,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44841,7 +44841,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45061,7 +45061,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45173,7 +45173,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45301,7 +45301,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45411,7 +45411,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45633,7 +45633,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45743,7 +45743,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45855,7 +45855,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45983,7 +45983,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46093,7 +46093,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46205,7 +46205,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46315,7 +46315,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46535,7 +46535,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46635,7 +46635,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46745,7 +46745,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46845,7 +46845,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46955,7 +46955,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47083,7 +47083,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47193,7 +47193,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47303,7 +47303,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47413,7 +47413,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47523,7 +47523,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47633,7 +47633,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47743,7 +47743,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47853,7 +47853,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47963,7 +47963,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48091,7 +48091,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48203,7 +48203,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48303,7 +48303,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48413,7 +48413,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48527,7 +48527,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48637,7 +48637,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48737,7 +48737,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48849,7 +48849,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48961,7 +48961,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49183,7 +49183,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49295,7 +49295,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49405,7 +49405,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49533,7 +49533,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49665,7 +49665,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49797,7 +49797,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49929,7 +49929,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50053,7 +50053,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50165,7 +50165,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50265,7 +50265,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50385,7 +50385,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50501,7 +50501,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50613,7 +50613,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50735,7 +50735,7 @@
       <c r="AD439" t="inlineStr"/>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50847,7 +50847,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50957,7 +50957,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51177,7 +51177,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51287,7 +51287,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51415,7 +51415,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51531,7 +51531,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51641,7 +51641,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51769,7 +51769,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51897,7 +51897,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52025,7 +52025,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52153,7 +52153,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52265,7 +52265,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52375,7 +52375,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52503,7 +52503,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52615,7 +52615,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52727,7 +52727,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52843,7 +52843,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52955,7 +52955,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53067,7 +53067,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53179,7 +53179,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53291,7 +53291,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53411,7 +53411,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53521,7 +53521,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53649,7 +53649,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53769,7 +53769,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53881,7 +53881,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53993,7 +53993,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54209,7 +54209,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54319,7 +54319,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54431,7 +54431,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54541,7 +54541,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54653,7 +54653,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54865,7 +54865,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54975,7 +54975,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55087,7 +55087,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55197,7 +55197,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55307,7 +55307,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55419,7 +55419,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55529,7 +55529,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55639,7 +55639,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55749,7 +55749,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55993,7 +55993,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56103,7 +56103,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56325,7 +56325,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56437,7 +56437,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56549,7 +56549,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56659,7 +56659,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56769,7 +56769,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56879,7 +56879,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56989,7 +56989,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57099,7 +57099,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57209,7 +57209,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57321,7 +57321,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57433,7 +57433,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57545,7 +57545,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57655,7 +57655,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57767,7 +57767,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57867,7 +57867,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57977,7 +57977,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58077,7 +58077,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58177,7 +58177,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58289,7 +58289,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58401,7 +58401,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58513,7 +58513,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58623,7 +58623,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58733,7 +58733,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58843,7 +58843,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58955,7 +58955,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59175,7 +59175,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59285,7 +59285,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59395,7 +59395,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59507,7 +59507,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59619,7 +59619,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59863,7 +59863,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59975,7 +59975,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60085,7 +60085,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60205,7 +60205,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60315,7 +60315,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60425,7 +60425,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60535,7 +60535,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60655,7 +60655,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60771,7 +60771,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60883,7 +60883,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61003,7 +61003,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61115,7 +61115,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61215,7 +61215,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61335,7 +61335,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61445,7 +61445,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61557,7 +61557,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61673,7 +61673,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61785,7 +61785,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61897,7 +61897,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62025,7 +62025,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62135,7 +62135,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62245,7 +62245,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62355,7 +62355,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62467,7 +62467,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62595,7 +62595,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62707,7 +62707,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62819,7 +62819,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62931,7 +62931,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63031,7 +63031,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63141,7 +63141,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63251,7 +63251,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63351,7 +63351,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63461,7 +63461,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63589,7 +63589,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63699,7 +63699,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63811,7 +63811,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63921,7 +63921,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64033,7 +64033,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64143,7 +64143,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64253,7 +64253,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64353,7 +64353,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64463,7 +64463,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64575,7 +64575,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64685,7 +64685,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64795,7 +64795,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64905,7 +64905,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65015,7 +65015,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65125,7 +65125,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65235,7 +65235,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65335,7 +65335,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65445,7 +65445,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65555,7 +65555,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65667,7 +65667,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65777,7 +65777,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65889,7 +65889,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -65999,7 +65999,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66109,7 +66109,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66219,7 +66219,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66329,7 +66329,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66439,7 +66439,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66551,7 +66551,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66661,7 +66661,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66773,7 +66773,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66885,7 +66885,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -66995,7 +66995,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67107,7 +67107,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67219,7 +67219,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67329,7 +67329,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67439,7 +67439,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67549,7 +67549,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67659,7 +67659,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67759,7 +67759,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67871,7 +67871,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -67981,7 +67981,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68091,7 +68091,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68219,7 +68219,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68331,7 +68331,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68443,7 +68443,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68571,7 +68571,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68683,7 +68683,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68811,7 +68811,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68939,7 +68939,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69051,7 +69051,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69163,7 +69163,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69273,7 +69273,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69385,7 +69385,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69495,7 +69495,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69605,7 +69605,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69717,7 +69717,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69829,7 +69829,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69941,7 +69941,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70051,7 +70051,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70161,7 +70161,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70273,7 +70273,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70385,7 +70385,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70495,7 +70495,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70607,7 +70607,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70717,7 +70717,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70817,7 +70817,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70927,7 +70927,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71039,7 +71039,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71149,7 +71149,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71261,7 +71261,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71371,7 +71371,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71481,7 +71481,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71591,7 +71591,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71701,7 +71701,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71811,7 +71811,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71923,7 +71923,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72033,7 +72033,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72143,7 +72143,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72253,7 +72253,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72365,7 +72365,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72475,7 +72475,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72587,7 +72587,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72699,7 +72699,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72799,7 +72799,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72909,7 +72909,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73021,7 +73021,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73133,7 +73133,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73245,7 +73245,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73357,7 +73357,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73467,7 +73467,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73577,7 +73577,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73689,7 +73689,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73799,7 +73799,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73911,7 +73911,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74011,7 +74011,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74121,7 +74121,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74233,7 +74233,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74343,7 +74343,7 @@
       <c r="AD650" t="inlineStr"/>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-24 08:44:12</t>
+          <t>2026-09-24 13:44:44</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74455,7 +74455,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74567,7 +74567,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74677,7 +74677,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74789,7 +74789,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74889,7 +74889,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74989,7 +74989,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75089,7 +75089,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75201,7 +75201,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75301,7 +75301,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75411,7 +75411,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75511,7 +75511,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75623,7 +75623,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75735,7 +75735,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75847,7 +75847,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75959,7 +75959,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76059,7 +76059,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76171,7 +76171,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76281,7 +76281,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76393,7 +76393,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76493,7 +76493,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76593,7 +76593,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76693,7 +76693,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76793,7 +76793,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76905,7 +76905,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77017,7 +77017,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77117,7 +77117,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77227,7 +77227,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77339,7 +77339,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77451,7 +77451,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77563,7 +77563,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77675,7 +77675,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77787,7 +77787,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77899,7 +77899,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78011,7 +78011,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78111,7 +78111,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78211,7 +78211,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78323,7 +78323,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78423,7 +78423,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78523,7 +78523,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78623,7 +78623,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78733,7 +78733,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78833,7 +78833,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -78943,7 +78943,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79025,7 +79025,7 @@
       <c r="AD694" t="inlineStr"/>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79107,7 +79107,7 @@
       <c r="AD695" t="inlineStr"/>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79189,7 +79189,7 @@
       <c r="AD696" t="inlineStr"/>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79271,7 +79271,7 @@
       <c r="AD697" t="inlineStr"/>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:48</t>
+          <t>2026-09-24 13:44:24</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
